--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484346_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484346_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.8461</v>
+        <v>7.4207</v>
       </c>
       <c r="E2" t="n">
-        <v>3.7495</v>
+        <v>4.0322</v>
       </c>
       <c r="F2" t="n">
-        <v>4.0966</v>
+        <v>3.3885</v>
       </c>
       <c r="G2" t="n">
         <v>4.0941</v>
@@ -610,13 +610,13 @@
         <v>2.3441</v>
       </c>
       <c r="S2" t="n">
-        <v>1.7948</v>
+        <v>1.3694</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1127</v>
+        <v>0.17</v>
       </c>
       <c r="U2" t="n">
-        <v>1.9075</v>
+        <v>1.1994</v>
       </c>
       <c r="V2" t="n">
         <v>-0.3869</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.3544</v>
+        <v>5.4154</v>
       </c>
       <c r="E3" t="n">
-        <v>3.8771</v>
+        <v>3.8564</v>
       </c>
       <c r="F3" t="n">
-        <v>1.4773</v>
+        <v>1.559</v>
       </c>
       <c r="G3" t="n">
         <v>4.2646</v>
@@ -688,13 +688,13 @@
         <v>1.7581</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6405</v>
+        <v>0.7015</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1127</v>
+        <v>-0.1334</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7532</v>
+        <v>0.8349</v>
       </c>
       <c r="V3" t="n">
         <v>-0.3321</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.8511</v>
+        <v>3.4545</v>
       </c>
       <c r="E4" t="n">
-        <v>2.9537</v>
+        <v>2.4482</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8974</v>
+        <v>1.0063</v>
       </c>
       <c r="G4" t="n">
         <v>0.7681</v>
@@ -766,13 +766,13 @@
         <v>1.7581</v>
       </c>
       <c r="S4" t="n">
-        <v>1.3603</v>
+        <v>0.9637</v>
       </c>
       <c r="T4" t="n">
-        <v>0.9851</v>
+        <v>0.4795</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3752</v>
+        <v>0.4842</v>
       </c>
       <c r="V4" t="n">
         <v>0.9414</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. PORTALEZ MUR</t>
+          <t>P. GIMENO MARTIN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7236</v>
+        <v>1.6469</v>
       </c>
       <c r="E5" t="n">
-        <v>1.0959</v>
+        <v>1.4179</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6277</v>
+        <v>0.229</v>
       </c>
       <c r="G5" t="n">
-        <v>2.161</v>
+        <v>1.4484</v>
       </c>
       <c r="H5" t="n">
-        <v>1.0558</v>
+        <v>1.6782</v>
       </c>
       <c r="I5" t="n">
-        <v>1.1052</v>
+        <v>-0.2298</v>
       </c>
       <c r="J5" t="n">
-        <v>3.4646</v>
+        <v>2.0077</v>
       </c>
       <c r="K5" t="n">
-        <v>2.0888</v>
+        <v>2.6413</v>
       </c>
       <c r="L5" t="n">
-        <v>1.3758</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.3036</v>
+        <v>-0.5593</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.033</v>
+        <v>-0.9631999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2706</v>
+        <v>0.4039</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.5627</v>
+        <v>0.9767</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.9301</v>
+        <v>-0.9767</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3674</v>
+        <v>1.9534</v>
       </c>
       <c r="S5" t="n">
-        <v>1.1253</v>
+        <v>0.4952</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5614</v>
+        <v>-0.1127</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5639</v>
+        <v>0.6079</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-1.2735</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.4996</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.7731</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. GIMENO MARTIN</t>
+          <t>J. FERNANDEZ MANZANARES</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3624</v>
+        <v>1.4311</v>
       </c>
       <c r="E6" t="n">
-        <v>1.2969</v>
+        <v>3.0287</v>
       </c>
       <c r="F6" t="n">
-        <v>0.06560000000000001</v>
+        <v>-1.5976</v>
       </c>
       <c r="G6" t="n">
-        <v>1.4484</v>
+        <v>1.1648</v>
       </c>
       <c r="H6" t="n">
-        <v>1.6782</v>
+        <v>1.583</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2298</v>
+        <v>-0.4183</v>
       </c>
       <c r="J6" t="n">
-        <v>2.0077</v>
+        <v>4.2313</v>
       </c>
       <c r="K6" t="n">
-        <v>2.6413</v>
+        <v>3.0302</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.6336000000000001</v>
+        <v>1.2011</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.5593</v>
+        <v>-3.0666</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.9631999999999999</v>
+        <v>-1.4472</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4039</v>
+        <v>-1.6194</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9767</v>
+        <v>0.3907</v>
       </c>
       <c r="Q6" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R6" t="n">
-        <v>1.9534</v>
+        <v>1.3674</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2108</v>
+        <v>-0.06950000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2337</v>
+        <v>-0.7255</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4445</v>
+        <v>0.656</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.2735</v>
+        <v>-0.0549</v>
       </c>
       <c r="W6" t="n">
         <v>0.4996</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.7731</v>
+        <v>-0.5545</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. FERNANDEZ MANZANARES</t>
+          <t>M. PORTALEZ MUR</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9674</v>
+        <v>1.2379</v>
       </c>
       <c r="E7" t="n">
-        <v>2.4833</v>
+        <v>0.6102</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.5159</v>
+        <v>0.6277</v>
       </c>
       <c r="G7" t="n">
-        <v>1.1648</v>
+        <v>2.161</v>
       </c>
       <c r="H7" t="n">
-        <v>1.583</v>
+        <v>1.0558</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4183</v>
+        <v>1.1052</v>
       </c>
       <c r="J7" t="n">
-        <v>4.2313</v>
+        <v>3.4646</v>
       </c>
       <c r="K7" t="n">
-        <v>3.0302</v>
+        <v>2.0888</v>
       </c>
       <c r="L7" t="n">
-        <v>1.2011</v>
+        <v>1.3758</v>
       </c>
       <c r="M7" t="n">
-        <v>-3.0666</v>
+        <v>-1.3036</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.4472</v>
+        <v>-1.033</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.6194</v>
+        <v>-0.2706</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3907</v>
+        <v>-1.5627</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9767</v>
+        <v>-2.9301</v>
       </c>
       <c r="R7" t="n">
         <v>1.3674</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5332</v>
+        <v>0.6397</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.271</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>0.7377</v>
+        <v>0.5639</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.0549</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.4996</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.5545</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.0746</v>
+        <v>-1.4964</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.683</v>
+        <v>-1.9959</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6084000000000001</v>
+        <v>0.4994</v>
       </c>
       <c r="G8" t="n">
         <v>-0.9626</v>
@@ -1078,13 +1078,13 @@
         <v>2.1488</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0534</v>
+        <v>0.5248</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.9078000000000001</v>
+        <v>-0.2207</v>
       </c>
       <c r="U8" t="n">
-        <v>0.8544</v>
+        <v>0.7455000000000001</v>
       </c>
       <c r="V8" t="n">
         <v>-0.2772</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.2204</v>
+        <v>-1.9826</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.2451</v>
+        <v>-4.2251</v>
       </c>
       <c r="F9" t="n">
-        <v>2.0247</v>
+        <v>2.2426</v>
       </c>
       <c r="G9" t="n">
         <v>-1.6256</v>
@@ -1156,13 +1156,13 @@
         <v>1.9534</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3819</v>
+        <v>0.6197</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0083</v>
+        <v>0.0283</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3736</v>
+        <v>0.5915</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>O. LOPEZ SANCHEZ</t>
+          <t>M. PACÍFICO CANTARELLI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.9662</v>
+        <v>-2.4095</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.1357</v>
+        <v>-2.4104</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.8305</v>
+        <v>0.0009</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.0941</v>
+        <v>-0.6629</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2528</v>
+        <v>0.5513</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.3468</v>
+        <v>-1.2142</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1436</v>
+        <v>0.2264</v>
       </c>
       <c r="K10" t="n">
-        <v>0.7368</v>
+        <v>0.9005</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.5931999999999999</v>
+        <v>-0.6741</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.2377</v>
+        <v>-0.8893</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.484</v>
+        <v>-0.3492</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.7536</v>
+        <v>-0.5401</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.586</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3907</v>
+        <v>1.5627</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2861</v>
+        <v>0.5269</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3026</v>
+        <v>-0.0192</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0165</v>
+        <v>0.5461</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-1.8828</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>-0.6642</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. PACÍFICO CANTARELLI</t>
+          <t>O. LOPEZ SANCHEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.0651</v>
+        <v>-2.7289</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.8754</v>
+        <v>-1.0346</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.1897</v>
+        <v>-1.6943</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.6629</v>
+        <v>-2.0941</v>
       </c>
       <c r="H11" t="n">
-        <v>0.5513</v>
+        <v>0.2528</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.2142</v>
+        <v>-2.3468</v>
       </c>
       <c r="J11" t="n">
-        <v>0.2264</v>
+        <v>0.1436</v>
       </c>
       <c r="K11" t="n">
-        <v>0.9005</v>
+        <v>0.7368</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.6741</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.8893</v>
+        <v>-2.2377</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.3492</v>
+        <v>-0.484</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.5401</v>
+        <v>-1.7536</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.3907</v>
+        <v>-0.586</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5627</v>
+        <v>0.3907</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1288</v>
+        <v>-0.0488</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4842</v>
+        <v>-0.2015</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3554</v>
+        <v>0.1527</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.8828</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.6642</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>10.7787</v>
+        <v>11.9891</v>
       </c>
       <c r="E12" t="n">
-        <v>4.5172</v>
+        <v>5.727599999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>6.2616</v>
+        <v>6.2615</v>
       </c>
       <c r="G12" t="n">
         <v>8.555799999999998</v>
@@ -1381,7 +1381,7 @@
         <v>-3.378299999999999</v>
       </c>
       <c r="P12" t="n">
-        <v>0.9768000000000001</v>
+        <v>0.9768000000000004</v>
       </c>
       <c r="Q12" t="n">
         <v>-15.6272</v>
@@ -1390,13 +1390,13 @@
         <v>16.6041</v>
       </c>
       <c r="S12" t="n">
-        <v>4.512099999999999</v>
+        <v>5.722600000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.8699</v>
+        <v>-0.6594</v>
       </c>
       <c r="U12" t="n">
-        <v>6.3819</v>
+        <v>6.382100000000001</v>
       </c>
       <c r="V12" t="n">
         <v>-3.266</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.9985</v>
+        <v>3.559</v>
       </c>
       <c r="E13" t="n">
-        <v>3.5486</v>
+        <v>3.2453</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4499</v>
+        <v>0.3137</v>
       </c>
       <c r="G13" t="n">
         <v>0.2393</v>
@@ -1468,13 +1468,13 @@
         <v>1.5627</v>
       </c>
       <c r="S13" t="n">
-        <v>0.3137</v>
+        <v>-0.1258</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.5831</v>
+        <v>-0.8864</v>
       </c>
       <c r="U13" t="n">
-        <v>0.8968</v>
+        <v>0.7606000000000001</v>
       </c>
       <c r="V13" t="n">
         <v>1.8828</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.2034</v>
+        <v>1.7095</v>
       </c>
       <c r="E14" t="n">
-        <v>3.2185</v>
+        <v>2.9152</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.0151</v>
+        <v>-1.2057</v>
       </c>
       <c r="G14" t="n">
         <v>2.2391</v>
@@ -1546,13 +1546,13 @@
         <v>2.3441</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.3362</v>
+        <v>-0.8302</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4621</v>
+        <v>-0.7654</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1258</v>
+        <v>-0.0648</v>
       </c>
       <c r="V14" t="n">
         <v>0.8865</v>
@@ -1579,10 +1579,10 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.4892</v>
+        <v>-0.388</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.1169</v>
+        <v>-1.0158</v>
       </c>
       <c r="F15" t="n">
         <v>0.6278</v>
@@ -1624,10 +1624,10 @@
         <v>0.7814</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1816</v>
+        <v>-0.0805</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.5447</v>
+        <v>-0.4436</v>
       </c>
       <c r="U15" t="n">
         <v>0.3631</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.7927</v>
+        <v>-0.536</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.747</v>
+        <v>-0.5448</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.0457</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="G16" t="n">
         <v>-1.7406</v>
@@ -1702,13 +1702,13 @@
         <v>2.7348</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.9266</v>
+        <v>-0.6699000000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.4388</v>
+        <v>-1.2365</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5121</v>
+        <v>0.5666</v>
       </c>
       <c r="V16" t="n">
         <v>3.0466</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>G. CATANY BIGAS</t>
+          <t>P. TABERNER PERALTA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,58 +1735,58 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.1418</v>
+        <v>-1.2392</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.7942</v>
+        <v>-1.0368</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6524</v>
+        <v>-0.2023</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.7009</v>
+        <v>-0.6229</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.8227</v>
+        <v>-0.7982</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1218</v>
+        <v>0.1753</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.5232</v>
+        <v>0.0609</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.5104</v>
+        <v>0.0205</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.0128</v>
+        <v>0.0405</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.1777</v>
+        <v>-0.6838</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.3123</v>
+        <v>-0.8186</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1346</v>
+        <v>0.1348</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9767</v>
+        <v>-0.586</v>
       </c>
       <c r="Q17" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R17" t="n">
-        <v>1.9534</v>
+        <v>0.3907</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4176</v>
+        <v>-0.0303</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2943</v>
+        <v>-0.121</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1233</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. TABERNER PERALTA</t>
+          <t>G. CATANY BIGAS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,58 +1813,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.2936</v>
+        <v>-1.2545</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.0368</v>
+        <v>-2.0975</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.2568</v>
+        <v>0.843</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.6229</v>
+        <v>-1.7009</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.7982</v>
+        <v>-1.8227</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1753</v>
+        <v>0.1218</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0609</v>
+        <v>-0.5232</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0205</v>
+        <v>-0.5104</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0405</v>
+        <v>-0.0128</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.6838</v>
+        <v>-1.1777</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.8186</v>
+        <v>-1.3123</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1348</v>
+        <v>0.1346</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.586</v>
+        <v>0.9767</v>
       </c>
       <c r="Q18" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R18" t="n">
-        <v>0.3907</v>
+        <v>1.9534</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0847</v>
+        <v>-0.5303</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.121</v>
+        <v>-0.5976</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0363</v>
+        <v>0.0673</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. REBOLLO BONET</t>
+          <t>S. PONS AVECILLAS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.5047</v>
+        <v>-1.4069</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6556</v>
+        <v>-0.8745000000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.1603</v>
+        <v>-0.5324</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0805</v>
+        <v>-0.8502</v>
       </c>
       <c r="H19" t="n">
-        <v>0.5393</v>
+        <v>-1.3761</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.4587</v>
+        <v>0.5259</v>
       </c>
       <c r="J19" t="n">
-        <v>1.7182</v>
+        <v>0.1828</v>
       </c>
       <c r="K19" t="n">
-        <v>1.6373</v>
+        <v>0.0614</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0809</v>
+        <v>0.1214</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.6377</v>
+        <v>-1.033</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.098</v>
+        <v>-1.4375</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.5397</v>
+        <v>0.4045</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.586</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R19" t="n">
-        <v>0.3907</v>
+        <v>1.1721</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0578</v>
+        <v>-0.4395</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3631</v>
+        <v>-0.3225</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3053</v>
+        <v>-0.117</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.9414</v>
+        <v>0.6642</v>
       </c>
       <c r="W19" t="n">
-        <v>0.2772</v>
+        <v>1.2186</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2186</v>
+        <v>-0.5545</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S. PONS AVECILLAS</t>
+          <t>A. REBOLLO BONET</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.6442</v>
+        <v>-1.6409</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.9757</v>
+        <v>0.6556</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.6686</v>
+        <v>-2.2964</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.8502</v>
+        <v>0.0805</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.3761</v>
+        <v>0.5393</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5259</v>
+        <v>-0.4587</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1828</v>
+        <v>1.7182</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0614</v>
+        <v>1.6373</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1214</v>
+        <v>0.0809</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.033</v>
+        <v>-1.6377</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.4375</v>
+        <v>-1.098</v>
       </c>
       <c r="O20" t="n">
-        <v>0.4045</v>
+        <v>-0.5397</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.7814</v>
+        <v>-0.586</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1721</v>
+        <v>0.3907</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6768</v>
+        <v>-0.194</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4237</v>
+        <v>-0.3631</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2532</v>
+        <v>0.1691</v>
       </c>
       <c r="V20" t="n">
-        <v>0.6642</v>
+        <v>-0.9414</v>
       </c>
       <c r="W20" t="n">
-        <v>1.2186</v>
+        <v>0.2772</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.5545</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.2232</v>
+        <v>-2.1687</v>
       </c>
       <c r="E21" t="n">
         <v>-0.8705000000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.3527</v>
+        <v>-1.2982</v>
       </c>
       <c r="G21" t="n">
         <v>0.2131</v>
@@ -2092,13 +2092,13 @@
         <v>0.3907</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3544</v>
+        <v>-0.2999</v>
       </c>
       <c r="T21" t="n">
         <v>-0.1816</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1728</v>
+        <v>-0.1183</v>
       </c>
       <c r="V21" t="n">
         <v>-1.4959</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.6605</v>
+        <v>-3.4388</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.0834</v>
+        <v>-3.7801</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4229</v>
+        <v>0.3412</v>
       </c>
       <c r="G22" t="n">
         <v>-2.6704</v>
@@ -2170,13 +2170,13 @@
         <v>2.7348</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.8496</v>
+        <v>-0.628</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.3782</v>
+        <v>-1.0749</v>
       </c>
       <c r="U22" t="n">
-        <v>0.5286</v>
+        <v>0.4469</v>
       </c>
       <c r="V22" t="n">
         <v>0.0549</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.2307</v>
+        <v>-3.974</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.0596</v>
+        <v>-2.8573</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.1711</v>
+        <v>-1.1167</v>
       </c>
       <c r="G23" t="n">
         <v>-2.8215</v>
@@ -2248,13 +2248,13 @@
         <v>1.1721</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.9404</v>
+        <v>-0.6837</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5915</v>
+        <v>-0.3892</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3489</v>
+        <v>-0.2945</v>
       </c>
       <c r="V23" t="n">
         <v>-0.6642</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-10.7787</v>
+        <v>-10.7785</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.2614</v>
+        <v>-6.261200000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>-4.517300000000001</v>
+        <v>-4.5172</v>
       </c>
       <c r="G24" t="n">
         <v>-8.555899999999999</v>
@@ -2326,10 +2326,10 @@
         <v>15.6275</v>
       </c>
       <c r="S24" t="n">
-        <v>-4.512</v>
+        <v>-4.5121</v>
       </c>
       <c r="T24" t="n">
-        <v>-6.382099999999999</v>
+        <v>-6.381800000000001</v>
       </c>
       <c r="U24" t="n">
         <v>1.8698</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484346_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484346_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,11 +632,16 @@
       <c r="X2" t="n">
         <v>-1.2186</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484346_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>R. DÍAZ DEL VALLE</t>
+          <t>R. DIAZ DEL VALLE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,28 +653,28 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.4154</v>
+        <v>3.8805</v>
       </c>
       <c r="E3" t="n">
-        <v>3.8564</v>
+        <v>2.3215</v>
       </c>
       <c r="F3" t="n">
         <v>1.559</v>
       </c>
       <c r="G3" t="n">
-        <v>4.2646</v>
+        <v>2.7296</v>
       </c>
       <c r="H3" t="n">
-        <v>3.2397</v>
+        <v>1.7048</v>
       </c>
       <c r="I3" t="n">
         <v>1.0249</v>
       </c>
       <c r="J3" t="n">
-        <v>3.4706</v>
+        <v>1.9357</v>
       </c>
       <c r="K3" t="n">
-        <v>3.5239</v>
+        <v>1.989</v>
       </c>
       <c r="L3" t="n">
         <v>-0.0533</v>
@@ -704,6 +714,11 @@
       </c>
       <c r="X3" t="n">
         <v>-1.8279</v>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484346_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-0.2772</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484346_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,11 +881,16 @@
       <c r="X5" t="n">
         <v>-1.7731</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484346_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. FERNANDEZ MANZANARES</t>
+          <t>R. DÍAZ DEL VALLE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +902,78 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4311</v>
+        <v>1.5349</v>
       </c>
       <c r="E6" t="n">
-        <v>3.0287</v>
+        <v>1.5349</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.5976</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>1.1648</v>
+        <v>1.5349</v>
       </c>
       <c r="H6" t="n">
-        <v>1.583</v>
+        <v>1.5349</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4183</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>4.2313</v>
+        <v>1.5349</v>
       </c>
       <c r="K6" t="n">
-        <v>3.0302</v>
+        <v>1.5349</v>
       </c>
       <c r="L6" t="n">
-        <v>1.2011</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-3.0666</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.4472</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.6194</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3907</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3674</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.06950000000000001</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7255</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0.656</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.0549</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.4996</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.5545</v>
+        <v>0</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484346_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. PORTALEZ MUR</t>
+          <t>J. FERNANDEZ MANZANARES</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +985,78 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2379</v>
+        <v>1.4311</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6102</v>
+        <v>3.0287</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6277</v>
+        <v>-1.5976</v>
       </c>
       <c r="G7" t="n">
-        <v>2.161</v>
+        <v>1.1648</v>
       </c>
       <c r="H7" t="n">
-        <v>1.0558</v>
+        <v>1.583</v>
       </c>
       <c r="I7" t="n">
-        <v>1.1052</v>
+        <v>-0.4183</v>
       </c>
       <c r="J7" t="n">
-        <v>3.4646</v>
+        <v>4.2313</v>
       </c>
       <c r="K7" t="n">
-        <v>2.0888</v>
+        <v>3.0302</v>
       </c>
       <c r="L7" t="n">
-        <v>1.3758</v>
+        <v>1.2011</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.3036</v>
+        <v>-3.0666</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.033</v>
+        <v>-1.4472</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.2706</v>
+        <v>-1.6194</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.5627</v>
+        <v>0.3907</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.9301</v>
+        <v>-0.9767</v>
       </c>
       <c r="R7" t="n">
         <v>1.3674</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6397</v>
+        <v>-0.06950000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>0.07580000000000001</v>
+        <v>-0.7255</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5639</v>
+        <v>0.656</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-0.0549</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.4996</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.5545</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484346_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. CAJAL PENACHO</t>
+          <t>M. PORTALEZ MUR</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1068,78 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.4964</v>
+        <v>1.2379</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.9959</v>
+        <v>0.6102</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4994</v>
+        <v>0.6277</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.9626</v>
+        <v>2.161</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2648</v>
+        <v>1.0558</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.2274</v>
+        <v>1.1052</v>
       </c>
       <c r="J8" t="n">
-        <v>1.155</v>
+        <v>3.4646</v>
       </c>
       <c r="K8" t="n">
-        <v>1.1678</v>
+        <v>2.0888</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.0128</v>
+        <v>1.3758</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.1176</v>
+        <v>-1.3036</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.903</v>
+        <v>-1.033</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.2146</v>
+        <v>-0.2706</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.7814</v>
+        <v>-1.5627</v>
       </c>
       <c r="Q8" t="n">
         <v>-2.9301</v>
       </c>
       <c r="R8" t="n">
-        <v>2.1488</v>
+        <v>1.3674</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5248</v>
+        <v>0.6397</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2207</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>0.7455000000000001</v>
+        <v>0.5639</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484346_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>N. CLEDJO HOUNGUES</t>
+          <t>M. PACÍFICO CANTARELLI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1151,78 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.9826</v>
+        <v>0.614</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.2251</v>
+        <v>0.614</v>
       </c>
       <c r="F9" t="n">
-        <v>2.2426</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.6256</v>
+        <v>0.614</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.2206</v>
+        <v>0.614</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4051</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.9363</v>
+        <v>0.614</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.9363</v>
+        <v>0.614</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.6893</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2842</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.4051</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.9301</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.9534</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6197</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0283</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5915</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.3869</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0.3869</v>
+        <v>0</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484346_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. PACÍFICO CANTARELLI</t>
+          <t>D. CAJAL PENACHO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1234,78 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.4095</v>
+        <v>-1.4964</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.4104</v>
+        <v>-1.9959</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0009</v>
+        <v>0.4994</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.6629</v>
+        <v>-0.9626</v>
       </c>
       <c r="H10" t="n">
-        <v>0.5513</v>
+        <v>0.2648</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.2142</v>
+        <v>-1.2274</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2264</v>
+        <v>1.155</v>
       </c>
       <c r="K10" t="n">
-        <v>0.9005</v>
+        <v>1.1678</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6741</v>
+        <v>-0.0128</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.8893</v>
+        <v>-2.1176</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.3492</v>
+        <v>-0.903</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.5401</v>
+        <v>-1.2146</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.3907</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.9534</v>
+        <v>-2.9301</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5627</v>
+        <v>2.1488</v>
       </c>
       <c r="S10" t="n">
-        <v>0.5269</v>
+        <v>0.5248</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0192</v>
+        <v>-0.2207</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5461</v>
+        <v>0.7455000000000001</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.8828</v>
+        <v>-0.2772</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.6642</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.2186</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484346_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>O. LOPEZ SANCHEZ</t>
+          <t>N. CLEDJO HOUNGUES</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1317,78 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.7289</v>
+        <v>-1.9826</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.0346</v>
+        <v>-4.2251</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.6943</v>
+        <v>2.2426</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.0941</v>
+        <v>-1.6256</v>
       </c>
       <c r="H11" t="n">
-        <v>0.2528</v>
+        <v>-1.2206</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.3468</v>
+        <v>-0.4051</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1436</v>
+        <v>-0.9363</v>
       </c>
       <c r="K11" t="n">
-        <v>0.7368</v>
+        <v>-0.9363</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.5931999999999999</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.2377</v>
+        <v>-0.6893</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.484</v>
+        <v>-0.2842</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.7536</v>
+        <v>-0.4051</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.586</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9767</v>
+        <v>-2.9301</v>
       </c>
       <c r="R11" t="n">
-        <v>0.3907</v>
+        <v>1.9534</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0488</v>
+        <v>0.6197</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2015</v>
+        <v>0.0283</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1527</v>
+        <v>0.5915</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>-0.3869</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>0.3869</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484346_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>O. LOPEZ SANCHEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,229 +1400,240 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>11.9891</v>
+        <v>-2.7289</v>
       </c>
       <c r="E12" t="n">
-        <v>5.727599999999999</v>
+        <v>-1.0346</v>
       </c>
       <c r="F12" t="n">
-        <v>6.2615</v>
+        <v>-1.6943</v>
       </c>
       <c r="G12" t="n">
-        <v>8.555799999999998</v>
+        <v>-2.0941</v>
       </c>
       <c r="H12" t="n">
-        <v>9.9079</v>
+        <v>0.2528</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.3522</v>
+        <v>-2.3468</v>
       </c>
       <c r="J12" t="n">
-        <v>18.5202</v>
+        <v>0.1436</v>
       </c>
       <c r="K12" t="n">
-        <v>16.494</v>
+        <v>0.7368</v>
       </c>
       <c r="L12" t="n">
-        <v>2.0262</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>-9.964500000000001</v>
+        <v>-2.2377</v>
       </c>
       <c r="N12" t="n">
-        <v>-6.5861</v>
+        <v>-0.484</v>
       </c>
       <c r="O12" t="n">
-        <v>-3.378299999999999</v>
+        <v>-1.7536</v>
       </c>
       <c r="P12" t="n">
-        <v>0.9768000000000004</v>
+        <v>-0.586</v>
       </c>
       <c r="Q12" t="n">
-        <v>-15.6272</v>
+        <v>-0.9767</v>
       </c>
       <c r="R12" t="n">
-        <v>16.6041</v>
+        <v>0.3907</v>
       </c>
       <c r="S12" t="n">
-        <v>5.722600000000001</v>
+        <v>-0.0488</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6594</v>
+        <v>-0.2015</v>
       </c>
       <c r="U12" t="n">
-        <v>6.382100000000001</v>
+        <v>0.1527</v>
       </c>
       <c r="V12" t="n">
-        <v>-3.266</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>3.4943</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-6.760199999999999</v>
+        <v>0</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484346_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>M. DIALLO BADJI</t>
+          <t>M. PACIFICO CANTARELLI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CB ANDRATX</t>
+          <t>C.B. CUARTE DE HUERVA</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.559</v>
+        <v>-3.0235</v>
       </c>
       <c r="E13" t="n">
-        <v>3.2453</v>
+        <v>-3.0244</v>
       </c>
       <c r="F13" t="n">
-        <v>0.3137</v>
+        <v>0.0009</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2393</v>
+        <v>-1.2768</v>
       </c>
       <c r="H13" t="n">
-        <v>1.7227</v>
+        <v>-0.06270000000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.4834</v>
+        <v>-1.2142</v>
       </c>
       <c r="J13" t="n">
-        <v>2.6358</v>
+        <v>-0.3876</v>
       </c>
       <c r="K13" t="n">
-        <v>3.1747</v>
+        <v>0.2865</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.5389</v>
+        <v>-0.6741</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.3966</v>
+        <v>-0.8893</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.452</v>
+        <v>-0.3492</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.9445</v>
+        <v>-0.5401</v>
       </c>
       <c r="P13" t="n">
-        <v>1.5627</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R13" t="n">
         <v>1.5627</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.1258</v>
+        <v>0.5269</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8864</v>
+        <v>-0.0192</v>
       </c>
       <c r="U13" t="n">
-        <v>0.7606000000000001</v>
+        <v>0.5461</v>
       </c>
       <c r="V13" t="n">
-        <v>1.8828</v>
+        <v>-1.8828</v>
       </c>
       <c r="W13" t="n">
-        <v>1.4959</v>
+        <v>-0.6642</v>
       </c>
       <c r="X13" t="n">
-        <v>0.3869</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484346_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. REDA COLL</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CB ANDRATX</t>
+          <t>C.B. CUARTE DE HUERVA</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.7095</v>
+        <v>11.9891</v>
       </c>
       <c r="E14" t="n">
-        <v>2.9152</v>
+        <v>5.727600000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.2057</v>
+        <v>6.2615</v>
       </c>
       <c r="G14" t="n">
-        <v>2.2391</v>
+        <v>8.5558</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.8491</v>
+        <v>9.907900000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>4.0882</v>
+        <v>-1.3522</v>
       </c>
       <c r="J14" t="n">
-        <v>5.1148</v>
+        <v>18.5202</v>
       </c>
       <c r="K14" t="n">
-        <v>0.3517</v>
+        <v>16.494</v>
       </c>
       <c r="L14" t="n">
-        <v>4.7631</v>
+        <v>2.0262</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.8757</v>
+        <v>-9.964500000000001</v>
       </c>
       <c r="N14" t="n">
-        <v>-2.2008</v>
+        <v>-6.5861</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.6749000000000001</v>
+        <v>-3.378299999999999</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.586</v>
+        <v>0.9768000000000006</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.9301</v>
+        <v>-15.6272</v>
       </c>
       <c r="R14" t="n">
-        <v>2.3441</v>
+        <v>16.6041</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.8302</v>
+        <v>5.7226</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.7654</v>
+        <v>-0.6594000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0648</v>
+        <v>6.3821</v>
       </c>
       <c r="V14" t="n">
-        <v>0.8865</v>
+        <v>-3.266</v>
       </c>
       <c r="W14" t="n">
-        <v>1.4959</v>
+        <v>3.4943</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.6093</v>
-      </c>
+        <v>-6.760199999999999</v>
+      </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. VAN ZUUREN ABAD</t>
+          <t>M. DIALLO BADJI</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1645,78 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.388</v>
+        <v>3.559</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.0158</v>
+        <v>3.2453</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6278</v>
+        <v>0.3137</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.9214</v>
+        <v>0.2393</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.0967</v>
+        <v>1.7227</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1753</v>
+        <v>-1.4834</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.5722</v>
+        <v>2.6358</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.6127</v>
+        <v>3.1747</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0405</v>
+        <v>-0.5389</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.3492</v>
+        <v>-2.3966</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.484</v>
+        <v>-1.452</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1348</v>
+        <v>-0.9445</v>
       </c>
       <c r="P15" t="n">
-        <v>0.7814</v>
+        <v>1.5627</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.7814</v>
+        <v>1.5627</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.0805</v>
+        <v>-0.1258</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4436</v>
+        <v>-0.8864</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3631</v>
+        <v>0.7606000000000001</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.1675</v>
+        <v>1.8828</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.4959</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.1675</v>
+        <v>0.3869</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484346_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>E. ZUSTOVICH</t>
+          <t>J. REDA COLL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1728,78 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.536</v>
+        <v>1.7095</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.5448</v>
+        <v>2.9152</v>
       </c>
       <c r="F16" t="n">
-        <v>0.008800000000000001</v>
+        <v>-1.2057</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.7406</v>
+        <v>2.2391</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.7552</v>
+        <v>-1.8491</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0146</v>
+        <v>4.0882</v>
       </c>
       <c r="J16" t="n">
-        <v>1.2748</v>
+        <v>5.1148</v>
       </c>
       <c r="K16" t="n">
-        <v>0.7201</v>
+        <v>0.3517</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5547</v>
+        <v>4.7631</v>
       </c>
       <c r="M16" t="n">
-        <v>-3.0154</v>
+        <v>-2.8757</v>
       </c>
       <c r="N16" t="n">
-        <v>-2.4753</v>
+        <v>-2.2008</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.5401</v>
+        <v>-0.6749000000000001</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.1721</v>
+        <v>-0.586</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.9069</v>
+        <v>-2.9301</v>
       </c>
       <c r="R16" t="n">
-        <v>2.7348</v>
+        <v>2.3441</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6699000000000001</v>
+        <v>-0.8302</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.2365</v>
+        <v>-0.7654</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5666</v>
+        <v>-0.0648</v>
       </c>
       <c r="V16" t="n">
-        <v>3.0466</v>
+        <v>0.8865</v>
       </c>
       <c r="W16" t="n">
-        <v>3.3238</v>
+        <v>1.4959</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2772</v>
+        <v>-0.6093</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484346_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P. TABERNER PERALTA</t>
+          <t>M. VAN ZUUREN ABAD</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.2392</v>
+        <v>-0.388</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.0368</v>
+        <v>-1.0158</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2023</v>
+        <v>0.6278</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.6229</v>
+        <v>-0.9214</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.7982</v>
+        <v>-1.0967</v>
       </c>
       <c r="I17" t="n">
         <v>0.1753</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0609</v>
+        <v>-0.5722</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0205</v>
+        <v>-0.6127</v>
       </c>
       <c r="L17" t="n">
         <v>0.0405</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.6838</v>
+        <v>-0.3492</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.8186</v>
+        <v>-0.484</v>
       </c>
       <c r="O17" t="n">
         <v>0.1348</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.586</v>
+        <v>0.7814</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.3907</v>
+        <v>0.7814</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0303</v>
+        <v>-0.0805</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.121</v>
+        <v>-0.4436</v>
       </c>
       <c r="U17" t="n">
-        <v>0.09080000000000001</v>
+        <v>0.3631</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-0.1675</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.1675</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484346_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>G. CATANY BIGAS</t>
+          <t>E. ZUSTOVICH</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.2545</v>
+        <v>-0.536</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.0975</v>
+        <v>-0.5448</v>
       </c>
       <c r="F18" t="n">
-        <v>0.843</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.7009</v>
+        <v>-1.7406</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.8227</v>
+        <v>-1.7552</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1218</v>
+        <v>0.0146</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.5232</v>
+        <v>1.2748</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.5104</v>
+        <v>0.7201</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.0128</v>
+        <v>0.5547</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.1777</v>
+        <v>-3.0154</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.3123</v>
+        <v>-2.4753</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1346</v>
+        <v>-0.5401</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9767</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9767</v>
+        <v>-3.9069</v>
       </c>
       <c r="R18" t="n">
-        <v>1.9534</v>
+        <v>2.7348</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5303</v>
+        <v>-0.6699000000000001</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5976</v>
+        <v>-1.2365</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0673</v>
+        <v>0.5666</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>3.0466</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>3.3238</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484346_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S. PONS AVECILLAS</t>
+          <t>P. TABERNER PERALTA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.4069</v>
+        <v>-1.2392</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.8745000000000001</v>
+        <v>-1.0368</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.5324</v>
+        <v>-0.2023</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.8502</v>
+        <v>-0.6229</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.3761</v>
+        <v>-0.7982</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5259</v>
+        <v>0.1753</v>
       </c>
       <c r="J19" t="n">
-        <v>0.1828</v>
+        <v>0.0609</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0614</v>
+        <v>0.0205</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1214</v>
+        <v>0.0405</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.033</v>
+        <v>-0.6838</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.4375</v>
+        <v>-0.8186</v>
       </c>
       <c r="O19" t="n">
-        <v>0.4045</v>
+        <v>0.1348</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.7814</v>
+        <v>-0.586</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1721</v>
+        <v>0.3907</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4395</v>
+        <v>-0.0303</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3225</v>
+        <v>-0.121</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.117</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="V19" t="n">
-        <v>0.6642</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.5545</v>
+        <v>0</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484346_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. REBOLLO BONET</t>
+          <t>G. CATANY BIGAS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.6409</v>
+        <v>-1.2545</v>
       </c>
       <c r="E20" t="n">
-        <v>0.6556</v>
+        <v>-2.0975</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.2964</v>
+        <v>0.843</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0805</v>
+        <v>-1.7009</v>
       </c>
       <c r="H20" t="n">
-        <v>0.5393</v>
+        <v>-1.8227</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.4587</v>
+        <v>0.1218</v>
       </c>
       <c r="J20" t="n">
-        <v>1.7182</v>
+        <v>-0.5232</v>
       </c>
       <c r="K20" t="n">
-        <v>1.6373</v>
+        <v>-0.5104</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0809</v>
+        <v>-0.0128</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.6377</v>
+        <v>-1.1777</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.098</v>
+        <v>-1.3123</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.5397</v>
+        <v>0.1346</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.586</v>
+        <v>0.9767</v>
       </c>
       <c r="Q20" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R20" t="n">
-        <v>0.3907</v>
+        <v>1.9534</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.194</v>
+        <v>-0.5303</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3631</v>
+        <v>-0.5976</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1691</v>
+        <v>0.0673</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.9414</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484346_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. BAUZA MEDINA</t>
+          <t>S. PONS AVECILLAS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.1687</v>
+        <v>-1.4069</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.8705000000000001</v>
+        <v>-0.8745000000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.2982</v>
+        <v>-0.5324</v>
       </c>
       <c r="G21" t="n">
-        <v>0.2131</v>
+        <v>-0.8502</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.0565</v>
+        <v>-1.3761</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2696</v>
+        <v>0.5259</v>
       </c>
       <c r="J21" t="n">
-        <v>0.2878</v>
+        <v>0.1828</v>
       </c>
       <c r="K21" t="n">
-        <v>0.2878</v>
+        <v>0.0614</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>0.1214</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.0747</v>
+        <v>-1.033</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.3443</v>
+        <v>-1.4375</v>
       </c>
       <c r="O21" t="n">
-        <v>0.2696</v>
+        <v>0.4045</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.586</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R21" t="n">
-        <v>0.3907</v>
+        <v>1.1721</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2999</v>
+        <v>-0.4395</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1816</v>
+        <v>-0.3225</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1183</v>
+        <v>-0.117</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.4959</v>
+        <v>0.6642</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.4959</v>
+        <v>-0.5545</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484346_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>I. MARTINEZ MESEGUER</t>
+          <t>A. REBOLLO BONET</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2226,78 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.4388</v>
+        <v>-1.6409</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.7801</v>
+        <v>0.6556</v>
       </c>
       <c r="F22" t="n">
-        <v>0.3412</v>
+        <v>-2.2964</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.6704</v>
+        <v>0.0805</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.8368</v>
+        <v>0.5393</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.8336</v>
+        <v>-0.4587</v>
       </c>
       <c r="J22" t="n">
-        <v>0.8891</v>
+        <v>1.7182</v>
       </c>
       <c r="K22" t="n">
-        <v>2.0478</v>
+        <v>1.6373</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.1587</v>
+        <v>0.0809</v>
       </c>
       <c r="M22" t="n">
-        <v>-3.5595</v>
+        <v>-1.6377</v>
       </c>
       <c r="N22" t="n">
-        <v>-2.8846</v>
+        <v>-1.098</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.6749000000000001</v>
+        <v>-0.5397</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.1953</v>
+        <v>-0.586</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.9301</v>
+        <v>-0.9767</v>
       </c>
       <c r="R22" t="n">
-        <v>2.7348</v>
+        <v>0.3907</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.628</v>
+        <v>-0.194</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.0749</v>
+        <v>-0.3631</v>
       </c>
       <c r="U22" t="n">
-        <v>0.4469</v>
+        <v>0.1691</v>
       </c>
       <c r="V22" t="n">
-        <v>0.0549</v>
+        <v>-0.9414</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.6642</v>
+        <v>0.2772</v>
       </c>
       <c r="X22" t="n">
-        <v>0.719</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484346_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>P. JOVER SANS</t>
+          <t>A. BAUZA MEDINA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2309,78 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.974</v>
+        <v>-2.1687</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.8573</v>
+        <v>-0.8705000000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.1167</v>
+        <v>-1.2982</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.8215</v>
+        <v>0.2131</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.5787</v>
+        <v>-0.0565</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.2428</v>
+        <v>0.2696</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.1045</v>
+        <v>0.2878</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.5921999999999999</v>
+        <v>0.2878</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.5122</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.717</v>
+        <v>-0.0747</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.9864</v>
+        <v>-0.3443</v>
       </c>
       <c r="O23" t="n">
-        <v>0.2694</v>
+        <v>0.2696</v>
       </c>
       <c r="P23" t="n">
-        <v>0.1953</v>
+        <v>-0.586</v>
       </c>
       <c r="Q23" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R23" t="n">
-        <v>1.1721</v>
+        <v>0.3907</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6837</v>
+        <v>-0.2999</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3892</v>
+        <v>-0.1816</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2945</v>
+        <v>-0.1183</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.6642</v>
+        <v>-1.4959</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.3869</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.2772</v>
+        <v>-1.4959</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484346_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>I. MARTINEZ MESEGUER</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,68 +2392,235 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
+        <v>-3.4388</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-3.7801</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.3412</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-2.6704</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-0.8368</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-1.8336</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.8891</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2.0478</v>
+      </c>
+      <c r="L24" t="n">
+        <v>-1.1587</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-3.5595</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-2.8846</v>
+      </c>
+      <c r="O24" t="n">
+        <v>-0.6749000000000001</v>
+      </c>
+      <c r="P24" t="n">
+        <v>-0.1953</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>-2.9301</v>
+      </c>
+      <c r="R24" t="n">
+        <v>2.7348</v>
+      </c>
+      <c r="S24" t="n">
+        <v>-0.628</v>
+      </c>
+      <c r="T24" t="n">
+        <v>-1.0749</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0.4469</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0.0549</v>
+      </c>
+      <c r="W24" t="n">
+        <v>-0.6642</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0.719</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484346_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>P. JOVER SANS</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>CB ANDRATX</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-3.974</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-2.8573</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-1.1167</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-2.8215</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-2.5787</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-0.2428</v>
+      </c>
+      <c r="J25" t="n">
+        <v>-1.1045</v>
+      </c>
+      <c r="K25" t="n">
+        <v>-0.5921999999999999</v>
+      </c>
+      <c r="L25" t="n">
+        <v>-0.5122</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-1.717</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-1.9864</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0.2694</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0.1953</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.1721</v>
+      </c>
+      <c r="S25" t="n">
+        <v>-0.6837</v>
+      </c>
+      <c r="T25" t="n">
+        <v>-0.3892</v>
+      </c>
+      <c r="U25" t="n">
+        <v>-0.2945</v>
+      </c>
+      <c r="V25" t="n">
+        <v>-0.6642</v>
+      </c>
+      <c r="W25" t="n">
+        <v>-0.3869</v>
+      </c>
+      <c r="X25" t="n">
+        <v>-0.2772</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484346_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>CB ANDRATX</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
         <v>-10.7785</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E26" t="n">
         <v>-6.261200000000001</v>
       </c>
-      <c r="F24" t="n">
+      <c r="F26" t="n">
         <v>-4.5172</v>
       </c>
-      <c r="G24" t="n">
+      <c r="G26" t="n">
         <v>-8.555899999999999</v>
       </c>
-      <c r="H24" t="n">
+      <c r="H26" t="n">
         <v>-9.907999999999999</v>
       </c>
-      <c r="I24" t="n">
+      <c r="I26" t="n">
         <v>1.3522</v>
       </c>
-      <c r="J24" t="n">
+      <c r="J26" t="n">
         <v>9.964300000000003</v>
       </c>
-      <c r="K24" t="n">
+      <c r="K26" t="n">
         <v>6.586</v>
       </c>
-      <c r="L24" t="n">
+      <c r="L26" t="n">
         <v>3.3785</v>
       </c>
-      <c r="M24" t="n">
+      <c r="M26" t="n">
         <v>-18.5203</v>
       </c>
-      <c r="N24" t="n">
+      <c r="N26" t="n">
         <v>-16.4938</v>
       </c>
-      <c r="O24" t="n">
+      <c r="O26" t="n">
         <v>-2.0264</v>
       </c>
-      <c r="P24" t="n">
+      <c r="P26" t="n">
         <v>-0.9766999999999997</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="Q26" t="n">
         <v>-16.604</v>
       </c>
-      <c r="R24" t="n">
+      <c r="R26" t="n">
         <v>15.6275</v>
       </c>
-      <c r="S24" t="n">
+      <c r="S26" t="n">
         <v>-4.5121</v>
       </c>
-      <c r="T24" t="n">
+      <c r="T26" t="n">
         <v>-6.381800000000001</v>
       </c>
-      <c r="U24" t="n">
+      <c r="U26" t="n">
         <v>1.8698</v>
       </c>
-      <c r="V24" t="n">
+      <c r="V26" t="n">
         <v>3.266000000000001</v>
       </c>
-      <c r="W24" t="n">
+      <c r="W26" t="n">
         <v>6.7603</v>
       </c>
-      <c r="X24" t="n">
+      <c r="X26" t="n">
         <v>-3.4943</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
